--- a/data/trans_dic/P25C$otrosprofesionales_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,62</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 10,06</t>
+          <t>2,04; 9,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,12</t>
+          <t>1,0; 4,08</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,84</t>
+          <t>0,0; 17,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,77</t>
+          <t>0,43; 3,59</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,21</t>
+          <t>0,93; 3,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,4</t>
+          <t>0,4; 1,41</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3980</t>
+          <t>0; 4731</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4207</t>
+          <t>0; 3967</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7267</t>
+          <t>0; 10075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 819</t>
+          <t>0; 841</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6998</t>
+          <t>0; 6910</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1763; 8671</t>
+          <t>1758; 8097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2383; 10007</t>
+          <t>2435; 9916</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3195</t>
+          <t>0; 3186</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2813</t>
+          <t>0; 3020</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4263</t>
+          <t>0; 4616</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3635</t>
+          <t>0; 4283</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2624</t>
+          <t>0; 3179</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>581; 5067</t>
+          <t>583; 4829</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>832; 9049</t>
+          <t>834; 9150</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3141; 10839</t>
+          <t>3137; 11316</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4438; 16629</t>
+          <t>4726; 16793</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otrosprofesionales_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Edad-trans_dic.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,39</t>
+          <t>1,97; 8,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,08</t>
+          <t>1,18; 4,83</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,98</t>
+          <t>0,0; 17,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,59</t>
+          <t>0,43; 3,64</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,3; 1,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,35</t>
+          <t>1,07; 3,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,41</t>
+          <t>0,72; 1,9</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>755</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>755</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3967</t>
+          <t>0; 3439</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1786</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 10075</t>
+          <t>0; 5475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 841</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6910</t>
+          <t>0; 6161</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>6206</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4622</t>
+          <t>0; 5701</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1758; 8097</t>
+          <t>1856; 8055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2435; 9916</t>
+          <t>3061; 12524</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>615</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1284</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3186</t>
+          <t>0; 3393</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 3198</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4616</t>
+          <t>0; 4038</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1985</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4283</t>
+          <t>0; 4211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 3439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>583; 4829</t>
+          <t>642; 5402</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>834; 9150</t>
+          <t>2000; 10157</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3137; 11316</t>
+          <t>3902; 12254</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4726; 16793</t>
+          <t>7383; 19530</t>
         </is>
       </c>
     </row>
